--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-von-se-betroffen.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-von-se-betroffen.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-von-se-betroffen.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-von-se-betroffen.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-von-se-betroffen.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-von-se-betroffen.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-von-se-betroffen.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-von-se-betroffen.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
